--- a/mode_docx_gen/pmi_ka/ka_modes/КА_28.xlsx
+++ b/mode_docx_gen/pmi_ka/ka_modes/КА_28.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -656,8 +656,8 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
+      <c r="R2" t="n">
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -806,16 +806,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
@@ -1173,8 +1173,8 @@
       <c r="AB2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" t="n">
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
